--- a/benchmark/dips_auditados.xlsx
+++ b/benchmark/dips_auditados.xlsx
@@ -567,11 +567,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T40S009CZ1T</t>
+          <t>T40S009DB2E</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DURING SV2 WAS FOUND STEP 3 FUMIGATION CERTIFICATE WITH LESS THAN 7 DAYS UNTIL EXPIRATION EXP: 13- AUG-2026 IAW TC B737-05-1-0001-U-JIC REV54 6/5/26 STEP 3. THIS ITEM ENTER DIP</t>
+          <t>CREW OXYGEN INDICATION WITH 900 PSI</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -593,17 +593,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HP-1830CMP</t>
+          <t>HP-9902CMP</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1830CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9902CMP</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -613,20 +613,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46247.99930555555</v>
+        <v>46250.99930555555</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>46244.20902777778</v>
+        <v>46247.07222222222</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>46244.55555555555</v>
+        <v>46247.58333333334</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -643,14 +643,14 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>DIP Completado. T/A Aperturado correctamente.</t>
+          <t>T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T40S009CXDT</t>
+          <t>T40S009CYP4</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DURING SVC 2 CREW OXY SYS WAS FOUND WITH 1,000 PSI</t>
+          <t>DIP - CREW OXYGEN BOTTLE WITH LOW PRESS</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HP-9812CMP</t>
+          <t>HP-1856CMP</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9812CMP</t>
+          <t>Boeing 737-8V3 - HP-1856CMP</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -712,20 +712,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35-DIP</t>
+          <t>35-dip</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46246.99930555555</v>
+        <v>46247.99930555555</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>46243.70277777778</v>
+        <v>46244.12916666667</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>46246.45833333334</v>
+        <v>46245.47916666666</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -737,12 +737,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>DISCREPANCIA NO CRÍTICA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente, faltan attachments</t>
+          <t>T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T3" t="b">
@@ -765,11 +765,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T40S009CKYW</t>
+          <t>T40S009CP7E</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -778,11 +778,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIP - FWD FAK</t>
+          <t>CREW OXYGEN BOTTLE WITH 950 PSI</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -791,17 +791,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HP-9917CMP</t>
+          <t>HP-1728CMP</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9917CMP</t>
+          <t>Boeing 737-86N - HP-1728CMP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -811,22 +811,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46295.99930555555</v>
+        <v>46244.99930555555</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>46240.66736111111</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46241.53125</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>46242.88888888889</v>
       </c>
       <c r="O4" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -834,7 +832,7 @@
         </is>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -843,7 +841,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Tarjeta ACTIVE. T/A aperturado correctamente</t>
+          <t>T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T4" t="b">
@@ -856,11 +854,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T40S009CHSE</t>
+          <t>T40S009CJ9B</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -869,11 +867,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIP - AFT UNIVERSAL PRECAUTION KIT S/N COPA174 DUE DATE 31-OCT-2026</t>
+          <t>During overnight cabin check was found CREW OXYGEN LESS THAN 1000 PSI</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -882,17 +880,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HP-1537CMP</t>
+          <t>HP-1833CMP</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1537CMP</t>
+          <t>Boeing 737-8V3 - HP-1833CMP</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -902,22 +900,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46326.99930555555</v>
+        <v>46243.99930555555</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>46240.20972222222</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46240.26111111111</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>46242.90972222222</v>
       </c>
       <c r="O5" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -925,7 +921,7 @@
         </is>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -940,18 +936,28 @@
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="U5" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T40S009CBG4</t>
+          <t>T40S009CHSE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -960,30 +966,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>During Task card B737-05-1-0001-U-Jic Step 29 Was found Brake 1 &lt;1/16 (0.0655) pulg.</t>
+          <t>DIP - AFT UNIVERSAL PRECAUTION KIT S/N COPA174 DUE DATE 31-OCT-2026</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CYCLES</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HP-1845CMP</t>
+          <t>HP-1537CMP</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1845CMP</t>
+          <t>Boeing 737-8V3 - HP-1537CMP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,20 +999,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46243.54722222222</v>
+        <v>46326.99930555555</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>46238.31666666667</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>46241.54166666666</v>
+        <v>46240.20972222222</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1014,35 +1022,29 @@
         </is>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>T/A aperturado correctamente</t>
+        </is>
+      </c>
       <c r="T6" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T40S009C70C</t>
+          <t>T40S009CCL4</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1055,11 +1057,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FUMIGATION CERTIFICATE WITH LESS THAN 7 DAYS REMAIN FOR DUE DATE 04-AUG-2026, OPEN DIP TO HAVE THE CERTIFICATE REPLACED</t>
+          <t>DIP - AFT UPK</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1068,17 +1070,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HP-9905CMP</t>
+          <t>HP-9907CMP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9905CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9907CMP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1092,16 +1094,18 @@
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46238.99930555555</v>
+        <v>46356.99930555555</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>46237.34930555556</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>46237.66666666666</v>
+        <v>46238.75833333333</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1118,30 +1122,24 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>DIP completado bajo los intervalos correctos</t>
+          <t>EVENTO SE ENCUENTRA ACTIVO</t>
         </is>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T40S009C6DB</t>
+          <t>T40S009CCKV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1150,11 +1148,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAREP - FWD POB HYDRO DUE DATE</t>
+          <t>DIP - FWD UPK</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1168,12 +1166,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HP-1525CMP</t>
+          <t>HP-9907CMP</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Boeing 737-7V3 - HP-1525CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9907CMP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1183,14 +1181,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>35-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
         <v>46295.99930555555</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>46237.25902777778</v>
+        <v>46238.75625</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1206,16 +1204,16 @@
         </is>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA NO CRÍTICA</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente.</t>
+          <t>DIP con T/A Incorrecto para Sep-2026 // UPK tiene shelf life expiry Sep- 2027</t>
         </is>
       </c>
       <c r="T8" t="b">
@@ -1228,11 +1226,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T40S009C4UR</t>
+          <t>T40S009CBG4</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1241,30 +1239,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AHM - 361 451 41/42 BLEED CTRL CARD L &amp; R scheduled maintenance task shows: SMT</t>
+          <t>During Task card B737-05-1-0001-U-Jic Step 29 Was found Brake 1 &lt;1/16 (0.0655) pulg.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2930</v>
+        <v>20</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HOUR</t>
+          <t>CYCLES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HP-9815CMP</t>
+          <t>HP-1845CMP</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9815CMP</t>
+          <t>Boeing 737-8V3 - HP-1845CMP</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1274,22 +1272,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>36-DIP</t>
+          <t>32-DIP</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46471.99930555555</v>
+        <v>46243.54722222222</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>46236.87083333333</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46238.31666666667</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>46241.54166666666</v>
       </c>
       <c r="O9" t="n">
-        <v>2796</v>
+        <v>6</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1297,33 +1293,39 @@
         </is>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DISCREPANCIA CRÍTICA</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>AMM indica RIR cada 70FH y no tiene, con TA de 3,000FH que discrepa en tarjeta active // SOLO SE REPORTA DIP INTERVAL INCORRECTO FALTA CONFIRMAR RIRs de 70 FH</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T40S009C048</t>
+          <t>T40S009CA8W</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1332,11 +1334,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DIP- WING SECTION AILERON CONTROL CABLE</t>
+          <t>DIP-AFT CABIN FIRT AID KIT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1350,12 +1352,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HP-1716CMP</t>
+          <t>HP-9803CMP</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1716CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9803CMP</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,14 +1367,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46417.99930555555</v>
+        <v>46356.99930555555</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>46235.36458333334</v>
+        <v>46238.19305555556</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1380,7 +1382,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1388,20 +1390,20 @@
         </is>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA NO CRÍTICA</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>DIP ABIERTO CORRECTAMENTE, SE MANTIENE ACTIVE CON DUE DATE BEFORE 30JAN2027</t>
+          <t>DIP SN INCORRECTO, SE PIDIÓ CORRECIÓN DE TARJETA DE LECTURA</t>
         </is>
       </c>
       <c r="T10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1410,7 +1412,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T40S009BX7N</t>
+          <t>T40S009C70C</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1423,11 +1425,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DIP-UNIVERVAL PRECAUTION KIT FWD PASSENGER CABIN</t>
+          <t>FUMIGATION CERTIFICATE WITH LESS THAN 7 DAYS REMAIN FOR DUE DATE 04-AUG-2026, OPEN DIP TO HAVE THE CERTIFICATE REPLACED</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1436,17 +1438,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HP-9911CMP</t>
+          <t>HP-9905CMP</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9911CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9905CMP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1460,18 +1462,16 @@
         </is>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46356.99930555555</v>
+        <v>46238.99930555555</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>46234.67430555556</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46237.34930555556</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>46237.66666666666</v>
       </c>
       <c r="O11" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1488,24 +1488,30 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>DIP completado bajo los intervalos correctos</t>
         </is>
       </c>
       <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T40S009BTKK</t>
+          <t>T40S009C6DB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1514,11 +1520,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DIP-EMERGENCY MEDICAL KIT</t>
+          <t>MAREP - FWD POB HYDRO DUE DATE</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1532,12 +1538,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HP-9910CMP</t>
+          <t>HP-1525CMP</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9910CMP</t>
+          <t>Boeing 737-7V3 - HP-1525CMP</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1547,14 +1553,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46356.99930555555</v>
+        <v>46295.99930555555</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46233.68055555555</v>
+        <v>46237.25902777778</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1562,7 +1568,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1570,7 +1576,7 @@
         </is>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1579,7 +1585,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>DIP ACTIVE. T/A aperturado correctamente aunque description señala fecha de expiración de 31-NOV-2026 y en Inventario 30-NOV-2026</t>
+          <t>T/A aperturado correctamente.</t>
         </is>
       </c>
       <c r="T12" t="b">
@@ -1592,11 +1598,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T40S009BP05</t>
+          <t>T40S009C4UR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1605,15 +1611,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DIP - RE-TENSION CHECK RH AILERON CABLE ABSB-R1</t>
+          <t>AHM - 361 451 41/42 BLEED CTRL CARD L &amp; R scheduled maintenance task shows: SMT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>184</v>
+        <v>2930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>HOUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1623,12 +1629,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HP-1849CMP</t>
+          <t>HP-9815CMP</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1849CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9815CMP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1638,14 +1644,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>05-DIP</t>
+          <t>36-DIP</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46416.99930555555</v>
+        <v>46471.99930555555</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46232.38402777778</v>
+        <v>46236.87083333333</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1653,7 +1659,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>170</v>
+        <v>2796</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1661,16 +1667,16 @@
         </is>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA CRÍTICA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>AMM indica RIR cada 70FH y no tiene, con TA de 3,000FH que discrepa en tarjeta active // SOLO SE REPORTA DIP INTERVAL INCORRECTO FALTA CONFIRMAR RIRs de 70 FH</t>
         </is>
       </c>
       <c r="T13" t="b">
@@ -1683,11 +1689,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T40S009BNX0</t>
+          <t>T40S009C19T</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1696,11 +1702,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DIP - CREW OXYGEN PREESURE SYSTEM</t>
+          <t>Fwd halon Fire Extinguisher bottle with less than 120 days of due date.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1709,17 +1715,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HP-9803CMP</t>
+          <t>HP-1723CMP</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9803CMP</t>
+          <t>Boeing 737-8V3 - HP-1723CMP</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1729,20 +1735,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>35-DIP</t>
+          <t>26-DIP</t>
         </is>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46235.99930555555</v>
+        <v>46319.99930555555</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46232.37777777778</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>46233.79166666666</v>
+        <v>46235.71388888889</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1750,7 +1758,7 @@
         </is>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1759,34 +1767,24 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+          <t>8130-3 INSP 24-OCT-2025 EN AIRVAULT</t>
         </is>
       </c>
       <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T40S009BMBW</t>
+          <t>T40S009BV2D</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1795,11 +1793,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE FUMIGACION</t>
+          <t>MAIN WHEEL ASSY #1 TIRE SHOW THE TREAD REINFORCEMENT, 1ST PLY DURING A TRHU-FLIGHT, A TIRE MAY CONTINUE IN SERVICE TO THE NEXT RON STATION WITH ONE OR BOTH OF THESE CONDITIONS PROVIDED MAINTENEX</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1813,12 +1811,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HP-1722CMP</t>
+          <t>HP-1718CMP</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1722CMP</t>
+          <t>Boeing 737-8V3 - HP-1718CMP</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1828,17 +1826,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>32-DIP</t>
         </is>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46235.99930555555</v>
+        <v>46234.99930555555</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46232.20555555556</v>
+        <v>46234.11458333334</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>46235.66666666666</v>
+        <v>46234.54166666666</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1849,7 +1847,7 @@
         </is>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1858,24 +1856,34 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>DIP ABIERTO Y COMPLETADO DENTRO DEL LÍMITE, NO SE ADJUNTA CERT DE FUMIGACIÓN VENCIDO</t>
+          <t>Se abrió DIP y se completó el mismo día, no hizo referencia a intervalos</t>
         </is>
       </c>
       <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T40S009BM50</t>
+          <t>T40S009BUL4</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1884,11 +1892,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>COCKPIT HALON EXTINGUISHER</t>
+          <t>DIP-UPK FWD with less than 130 days of Due Date</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1902,12 +1910,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HP-1724CMP</t>
+          <t>HP-1840CMP</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1724CMP</t>
+          <t>Boeing 737-8V3 - HP-1840CMP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1917,14 +1925,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46340.99930555555</v>
+        <v>46326.99930555555</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46232.16388888889</v>
+        <v>46233.98333333333</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1932,7 +1940,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1947,9 +1955,13 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>EVENTO SE ENCUENTRA ACTIVO</t>
+        </is>
+      </c>
       <c r="T16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1958,11 +1970,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T40S009BGVY</t>
+          <t>T40S009BTER</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1971,30 +1983,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Main wheel tire #2 TIRE SHOWS THE TREAD REINFORCEMENT, 1ST PLY</t>
+          <t>DIP-FIRST AID KIT FWD PASSENGER COMPARTMENT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CYCLES</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HP-1838CMP</t>
+          <t>HP-9910CMP</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1838CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9910CMP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2004,20 +2016,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46232.01666666667</v>
+        <v>46295.99930555555</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46231.15</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>46231.65277777778</v>
+        <v>46233.64027777778</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2025,7 +2039,7 @@
         </is>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2034,34 +2048,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>DIP Completado dentro del deadline</t>
-        </is>
-      </c>
-      <c r="T17" t="b">
-        <v>1</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T40S009BERX</t>
+          <t>T40S009BQGM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2070,11 +2072,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>foward cargo cilling shroud with damage.</t>
+          <t>AFT COMP NET</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2083,17 +2085,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>HP-9928CMP</t>
+          <t>HP-1377CMP</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9928CMP</t>
+          <t>Boeing 737-7V3 - HP-1377CMP</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2103,22 +2105,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46350.99930555555</v>
+        <v>46242.99930555555</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46230.63888888889</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46232.86388888889</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>46233.79236111111</v>
       </c>
       <c r="O18" t="n">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2135,11 +2135,11 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>DIP ACTIVE. T/A y RIR aperturado correctamente</t>
+          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T40S009B81K</t>
+          <t>T40S009BMBW</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2161,11 +2161,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIP - EMK</t>
+          <t>CERTIFICADO DE FUMIGACION</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HP-9801CMP</t>
+          <t>HP-1722CMP</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9801CMP</t>
+          <t>Boeing 737-8V3 - HP-1722CMP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2198,18 +2198,16 @@
         </is>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46356.99930555555</v>
+        <v>46235.99930555555</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46228.64236111111</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46232.20555555556</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>46235.66666666666</v>
       </c>
       <c r="O19" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2217,7 +2215,7 @@
         </is>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2226,7 +2224,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>DIP ABIERTO Y COMPLETADO DENTRO DEL LÍMITE, NO SE ADJUNTA CERT DE FUMIGACIÓN VENCIDO</t>
         </is>
       </c>
       <c r="T19" t="b">
@@ -2239,11 +2237,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T40S009B7WN</t>
+          <t>T40S009BM50</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2252,11 +2250,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DIP - CERTIFICATE OF FUMIGATION DUE DATE 01-AUG-2026</t>
+          <t>COCKPIT HALON EXTINGUISHER</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2265,17 +2263,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HP-9907CMP</t>
+          <t>HP-1724CMP</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9907CMP</t>
+          <t>Boeing 737-8V3 - HP-1724CMP</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2285,20 +2283,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>26-DIP</t>
         </is>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46235.99930555555</v>
+        <v>46340.99930555555</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46228.60069444445</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>46229.88541666666</v>
+        <v>46232.16388888889</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2306,20 +2306,16 @@
         </is>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>DIP ABIERTO Y COMPLETADO DENTRO DEL LÍMITE, NO SE ADJUNTA CERT DE FUMIGACIÓN VENCIDO</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2328,11 +2324,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T40S009B3D8</t>
+          <t>T40S009BDXS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2341,61 +2337,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IN REFERENCE Service Visit # 2 WAS FOUND Crew Oxygen System Pressure indication: 1050 PSI</t>
+          <t>DIP // CERTIFICATE OF FUMIGATION WITH DUE DATE 31-JUL-2026.</t>
         </is>
       </c>
       <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>HP-1524CMP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Boeing 737-7V3 - HP-1524CMP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DIP</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>25-DIP</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>46234.99930555555</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>46230.35763888889</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>46231.52083333334</v>
+      </c>
+      <c r="O21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>DAY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>HP-1729CMP</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Boeing 737-8V3 - HP-1729CMP</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>DIP</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>35-DIP</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>46230.99930555555</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>46227.32777777778</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>46230.05555555555</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Busqueda</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2404,34 +2400,24 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>DIP ABIERTO Y COMPLETADO DENTRO DEL LÍMITE, NO SE ADJUNTA CERT DE FUMIGACIÓN VENCIDO</t>
         </is>
       </c>
       <c r="T21" t="b">
         <v>0</v>
       </c>
-      <c r="U21" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T40S009B357</t>
+          <t>T40S009B6AW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2440,15 +2426,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUMIGATION CERTIFICATE WITH 7 DAYS OF DUE DATE</t>
+          <t>DIP MLG Brake assy #(3)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>CYCLES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2458,12 +2444,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HP-1843CMP</t>
+          <t>HP-1835CMP</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1843CMP</t>
+          <t>Boeing 737-8V3 - HP-1835CMP</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2473,20 +2459,20 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>32-DIP</t>
         </is>
       </c>
       <c r="L22" s="1" t="n">
-        <v>46233.99930555555</v>
+        <v>46232.99930555555</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46227.30347222222</v>
+        <v>46228.17430555556</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>46230.9375</v>
+        <v>46230.23263888889</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2501,26 +2487,32 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>DIP ABIERTO EN REF A WP DE SV POR MENOS DE 7 DIAS PARA EL DUE DATE DE FUMIGACION, SE COMPLETÓ 2 DÍAS POSTERIOR A LA APERTURA, NO SE ADJUNTA CERTIFICADO DE FUMIGACION RETIRADO</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="b">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="U22" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T40S009AXL6</t>
+          <t>T40S009B5XJ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2529,11 +2521,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DIP-Right Main Landing Gear Shock Strut - Service</t>
+          <t>DIP-BOROSCOPE DUE TO FOD IN ENGINE #1</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2547,12 +2539,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HP-9904CMP</t>
+          <t>HP-1535CMP</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9904CMP</t>
+          <t>Boeing 737-8V3 - HP-1535CMP</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2562,20 +2554,20 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>05-DIP</t>
         </is>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46233.15625</v>
+        <v>46229.69652777778</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>46225.79930555556</v>
+        <v>46228.09375</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>46230.1875</v>
+        <v>46228.99305555555</v>
       </c>
       <c r="O23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2583,7 +2575,7 @@
         </is>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2592,34 +2584,24 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
+          <t>DIP COMPLETADO // T/A doblelimitante aperturado correctamente al ESN 864293</t>
         </is>
       </c>
       <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T40S009AVLF</t>
+          <t>T40S009AXL6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2628,15 +2610,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DURING TASK B737-05-1-U-JIC SV # 2 Was found Certificate of Fumigation with less of 7 days remaining to due date. Current Fecha de vencimiento 26-JUL-2026</t>
+          <t>DIP-Right Main Landing Gear Shock Strut - Service</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>CYCLES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2646,12 +2628,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HP-1730CMP</t>
+          <t>HP-9904CMP</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1730CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9904CMP</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2661,20 +2643,20 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>32-DIP</t>
         </is>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46229.99930555555</v>
+        <v>46233.15625</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>46225.24444444444</v>
+        <v>46225.79930555556</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>46227.83333333334</v>
+        <v>46230.1875</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2691,24 +2673,34 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>DIP ABIERTO EN REF A WP DE SV POR MENOS DE 7 DIAS PARA EL DUE DATE DE FUMIGACION, SE COMPLETÓ 2 DÍAS POSTERIOR A LA APERTURA, NO SE ADJUNTA CERTIFICADO DE FUMIGACION RETIRADO</t>
+          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T24" t="b">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="U24" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T40S009AV9N</t>
+          <t>T40S009ASL4</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2717,11 +2709,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NLG SHOCK STRUT DIMENSION "X" LOW</t>
+          <t>In reference of MAX-05-1-0001-U-JIC Service Visit Check STEP 8 was found Crew Oxygen System flight compartment indication pressure below 1100 psi, open a 3-day DIP to replace the bottle</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2735,12 +2727,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HP-9810CMP</t>
+          <t>HP-9805CMP</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9810CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9805CMP</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2750,17 +2742,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>35-DIP</t>
         </is>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46226.99930555555</v>
+        <v>46227.99930555555</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>46225.20416666667</v>
+        <v>46224.40625</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>46226.20833333334</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2771,23 +2763,23 @@
         </is>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>DISCREPANCIA NO CRÍTICA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>El dip fue aperturado por 9 ciclos. Sin embargo, en scheduling aparece configurado por 1 día o 9 ciclos. De igual forma cerraron el dip antes de los 9 ciclos.</t>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
         </is>
       </c>
       <c r="T25" t="b">
         <v>0</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2803,11 +2795,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T40S009ARNX</t>
+          <t>T40S009ANN0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2816,7 +2808,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIP- DURING SERVICE VISIT # 3 WAS FOUND CERTIFICATE OF FUMIGATION ENTRY ON DIP DUE DATE 25-JUL-2026</t>
+          <t>DIP- FUEL MICROBIAL GROWTH INSPECT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2834,12 +2826,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HP-9819CMP</t>
+          <t>HP-9916CMP</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9819CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9916CMP</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2849,17 +2841,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>28-DIP</t>
         </is>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46228.99930555555</v>
+        <v>46227.99930555555</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>46224.31875</v>
+        <v>46223.72638888889</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>46227.82291666666</v>
+        <v>46227.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2879,20 +2871,30 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>DIP ABIERTO EN REF A WP DE SV POR MENOS DE 7 DIAS PARA EL DUE DATE DE FUMIGACION, SE COMPLETÓ 4 DÍAS POSTERIOR A LA APERTURA, NO SE ADJUNTA CERTIFICADO DE FUMIGACION RETIRADO</t>
+          <t>T/A Diferio correctamente dentro de los 4 días habiles y por un QC</t>
         </is>
       </c>
       <c r="T26" t="b">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="U26" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T40S009ANR9</t>
+          <t>T40S009AMA9</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2905,11 +2907,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DIP-AFT CABIN FIRT AID KIT</t>
+          <t>DIP-SURVIVAL KIT NEXT DUE DATE</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2923,12 +2925,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HP-9916CMP</t>
+          <t>HP-1712CMP</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9916CMP</t>
+          <t>Boeing 737-8V3 - HP-1712CMP</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2942,18 +2944,16 @@
         </is>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46295.99930555555</v>
+        <v>46274.99930555555</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>46223.76111111111</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46223.38055555556</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>46255.63819444444</v>
       </c>
       <c r="O27" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2961,31 +2961,37 @@
         </is>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA NO CRÍTICA</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>No S/N de botella en la descripción</t>
+        </is>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>PENDIENTES</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T40S009AMA9</t>
+          <t>T40S009AHFG</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2994,11 +3000,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DIP-SURVIVAL KIT NEXT DUE DATE</t>
+          <t>IN REF TO LOG T40S009AE87 LH PITOT REPLACEMENT, PERFORM SEALANT INSTALATION AS PER AMM TASK 27-31-94-400-801 Rev 28, 15 May 2026 , WITHIN 10 DAYS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3007,17 +3013,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HP-1712CMP</t>
+          <t>HP-9901CMP</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1712CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9901CMP</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3027,20 +3033,20 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>27-DIP</t>
         </is>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46274.99930555555</v>
+        <v>46232.99930555555</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>46223.38055555556</v>
+        <v>46222.28888888889</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>46255.63819444444</v>
+        <v>46231.5</v>
       </c>
       <c r="O28" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3052,33 +3058,35 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>DISCREPANCIA NO CRÍTICA</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>No S/N de botella en la descripción</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="b">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="1" t="n">
+        <v>46245</v>
+      </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>PENDIENTES</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T40S009AK8C</t>
+          <t>T40S009AENJ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3087,11 +3095,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DURING 360 WAS FOUND 980 PSI THE CREW OXYGEN BOTTLE</t>
+          <t>DIP - FLIGHT COMPARTMENT HALON FIRE EXTINGUISHER WITH LESS THAN 120 DAYS OF DUE DATE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3100,17 +3108,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HP-1538CMP</t>
+          <t>HP-1856CMP</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1538CMP</t>
+          <t>Boeing 737-8V3 - HP-1856CMP</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3120,20 +3128,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>35-DIP</t>
+          <t>26-DIP</t>
         </is>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46225.99930555555</v>
+        <v>46310.99930555555</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>46222.97152777778</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>46223.54166666666</v>
+        <v>46221.36111111111</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3141,7 +3151,7 @@
         </is>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3150,30 +3160,20 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
         </is>
       </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
-      <c r="U29" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T40S009AK5F</t>
+          <t>T40S009A52M</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CREW OXYGEN WITH 850 PSI</t>
+          <t>During the flight deck check was found the crew oxygen indication with 800 psi.</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HP-9813CMP</t>
+          <t>HP-1720CMP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9813CMP</t>
+          <t>Boeing 737-8V3 - HP-1720CMP</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46225.99930555555</v>
+        <v>46221.99930555555</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>46222.88055555556</v>
+        <v>46218.95138888889</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>46224.5</v>
+        <v>46221.91666666666</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46240</v>
+        <v>46231</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T30" t="b">
         <v>0</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3272,11 +3272,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T40S009AG7U</t>
+          <t>T40S0099YJF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3285,15 +3285,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIP - RIGHT MAIN LANDING GEAR SHOCK STRUT</t>
+          <t>DIP - CERTIFICADO DE FUMIGACION</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CYCLES</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HP-9809CMP</t>
+          <t>HP-9807CMP</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9809CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9807CMP</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3318,20 +3318,20 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46225.99930555555</v>
+        <v>46220.99930555555</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>46221.89652777778</v>
+        <v>46217.30902777778</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>46224.04166666666</v>
+        <v>46217.66666666666</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46242</v>
+        <v>46227</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3348,34 +3348,22 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
-        </is>
-      </c>
-      <c r="T31" t="b">
-        <v>0</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T40S009AFSN</t>
+          <t>T40S0099VZU</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3384,11 +3372,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIP - AILERON CONTROL CABLE RE-TENSION CHECK LH ABSA-1.</t>
+          <t>DIP - UNIVERSAL PROTECTION KIT S/N: COPA308 Due Date: 30-NOV-2026</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3402,12 +3390,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HP-1716CMP</t>
+          <t>HP-1852CMP</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1716CMP</t>
+          <t>Boeing 737-8V3 - HP-1852CMP</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3417,14 +3405,14 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>27-DIP</t>
+          <t>25-DIP</t>
         </is>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46404.99930555555</v>
+        <v>46356.99930555555</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>46221.74375</v>
+        <v>46216.78888888889</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3432,7 +3420,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3440,7 +3428,7 @@
         </is>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3449,12 +3437,10 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
-        </is>
-      </c>
-      <c r="T32" t="b">
-        <v>0</v>
-      </c>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
@@ -3462,11 +3448,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T40S009A5Z0</t>
+          <t>T40S0099VVF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3475,15 +3461,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIP- Right Main Landing Gear Shock Strut - Service</t>
+          <t>DIP - FDR - Report</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CYCLES</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3493,12 +3479,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HP-1712CMP</t>
+          <t>HP-1852CMP</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1712CMP</t>
+          <t>Boeing 737-8V3 - HP-1852CMP</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3508,20 +3494,20 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>32-DIP</t>
+          <t>31-DIP</t>
         </is>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46222.83194444444</v>
+        <v>46246.99930555555</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>46219.19305555556</v>
+        <v>46216.73611111111</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>46221.20833333334</v>
+        <v>46234.16666666666</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3529,7 +3515,7 @@
         </is>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3538,14 +3524,14 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
+          <t>T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T33" t="b">
         <v>0</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3561,7 +3547,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T40S009A2MK</t>
+          <t>T40S0099T40</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -3574,7 +3560,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Flight Compartment Crew Oxygen System Pressure indication: is below 1100 psi</t>
+          <t>CREW OXYGEN BOTTLE FOUND WITH 850 PSI</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3592,12 +3578,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HP-1716CMP</t>
+          <t>HP-1852CMP</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1716CMP</t>
+          <t>Boeing 737-8V3 - HP-1852CMP</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3611,16 +3597,16 @@
         </is>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46221.99930555555</v>
+        <v>46219.99930555555</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>46218.24791666667</v>
+        <v>46216.075</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>46220.83333333334</v>
+        <v>46216.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3628,7 +3614,7 @@
         </is>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3637,14 +3623,14 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente</t>
+          <t>DIP COMPLETE, T/A aperturado correctamente</t>
         </is>
       </c>
       <c r="T34" t="b">
         <v>0</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3653,18 +3639,18 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Completado correctamente</t>
+          <t>T/A Completado correctamente</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T40S0099W08</t>
+          <t>T40S0099S8X</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3673,30 +3659,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIP - UNIVERSAL PROTECTION KIT S/N: COPA-7 Due Date: 30-NOV-2026</t>
+          <t>DIP-NLG SHOCK STRUT PRESSURE AND X DIMENSION CHECK</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>140</v>
+        <v>10</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>CYCLES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HP-1852CMP</t>
+          <t>HP-9901CMP</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1852CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9901CMP</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3706,22 +3692,20 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>12-DIP</t>
         </is>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46356.99930555555</v>
+        <v>46219.73402777778</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46216.79305555556</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46215.7375</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>46219.1875</v>
       </c>
       <c r="O35" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3729,7 +3713,7 @@
         </is>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3738,22 +3722,34 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+          <t>T/A aperturado correctamente</t>
+        </is>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T40S0099VZU</t>
+          <t>T40S0099QSL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3762,30 +3758,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DIP - UNIVERSAL PROTECTION KIT S/N: COPA308 Due Date: 30-NOV-2026</t>
+          <t>RADOME INTERNAL INSPECTION DUE TO BIRDSTRIKE</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>CYCLES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HP-1852CMP</t>
+          <t>HP-1843CMP</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1852CMP</t>
+          <t>Boeing 737-8V3 - HP-1843CMP</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3795,22 +3791,20 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>05-DIP</t>
         </is>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46356.99930555555</v>
+        <v>46216.49722222222</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>46216.78888888889</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>46215.25625</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>46215.66666666666</v>
       </c>
       <c r="O36" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3818,7 +3812,7 @@
         </is>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46227</v>
+        <v>46217</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3827,10 +3821,12 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>DIP COMPLETADO // T/A aperturado correctamente // No EC/RA Extension</t>
+        </is>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
@@ -3838,7 +3834,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T40S0099V53</t>
+          <t>T40S0099MU7</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3851,7 +3847,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CREW OXYGEN BOTTLE PRESSURE</t>
+          <t>Flight Compartment Crew Oxygen System Pressure indication: 1020 psi open a 3-day DIP to replace the bottle</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3869,12 +3865,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HP-9918CMP</t>
+          <t>HP-9815CMP</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9918CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9815CMP</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3888,58 +3884,50 @@
         </is>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46219.99930555555</v>
+        <v>46217.99930555555</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>46216.47638888889</v>
+        <v>46214.29513888889</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>46220.13888888889</v>
+        <v>46214.66666666666</v>
       </c>
       <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Busqueda</t>
+        </is>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>T/A aperturado correctamente</t>
+        </is>
+      </c>
+      <c r="T37" t="b">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Busqueda</t>
-        </is>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente para 16-JUL-2026 // WP reprogramado para el 17-JUL-2026 3AM Cumplimiento en Negativo</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Completado correctamente</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T40S0099UVU</t>
+          <t>T40S0099L05</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -3948,11 +3936,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CREW OXYGEN BOTTLE PSI IND ON 750 PSI</t>
+          <t>DIP - ELEVATOR CONTROL CABLES EA AND EB RE-TENSION CHECK AND ADJUSTMENT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3961,17 +3949,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HP-1523CMP</t>
+          <t>HP-9818CMP</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1523CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9818CMP</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3981,20 +3969,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>35-DIP</t>
+          <t>27-DIP</t>
         </is>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46219.99930555555</v>
+        <v>46397.99930555555</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>46216.38472222222</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>46218.1375</v>
+        <v>46213.86319444444</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -4002,7 +3992,7 @@
         </is>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4011,32 +4001,24 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>DIP COMPLETADO // T/A aperturado correctamente</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>T/A Completado correctamente</t>
-        </is>
-      </c>
+          <t>T/A aperturado correctamente</t>
+        </is>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T40S0099PNR</t>
+          <t>T40S0099K9B</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4045,11 +4027,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DIP-PORTABLE ELT</t>
+          <t>DIP - FIXED ELT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,12 +4045,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HP-1726CMP</t>
+          <t>HP-1845CMP</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Boeing 737-86N - HP-1726CMP</t>
+          <t>Boeing 737-8V3 - HP-1845CMP</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4078,14 +4060,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25-DIP</t>
+          <t>23-DIP</t>
         </is>
       </c>
       <c r="L39" s="1" t="n">
         <v>46418.99930555555</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>46214.87222222222</v>
+        <v>46213.64861111111</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -4121,11 +4103,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T40S009DHK0</t>
+          <t>T40S0099HMA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4134,30 +4116,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AVIONIC - FLAP/SLAT PROXIMITY SENSOR OUT OF RANGE ON RH WING</t>
+          <t>CERTIFICATE OF FUMIGATION DUE 16-JUL-26</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HOURS</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HP-9812CMP</t>
+          <t>HP-1849CMP</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9812CMP</t>
+          <t>Boeing 737-8V3 - HP-1849CMP</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4165,42 +4147,60 @@
           <t>DIP</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25-DIP</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>46219.99930555555</v>
+      </c>
       <c r="M40" s="1" t="n">
-        <v>46248.6875</v>
+        <v>46213.23194444444</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>46290.99930555555</v>
+        <v>46217.63194444445</v>
       </c>
       <c r="O40" t="n">
-        <v>468.97</v>
+        <v>2</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46253</v>
+        <v>46217</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>DISCREPANCIA NO CRÍTICA</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="b">
-        <v>0</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Completado correctamente</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T40S009DN7C</t>
+          <t>T40S0099GMS</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -4213,15 +4213,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DIP-CURRENT CERTIFICATE OF FUMIGATION</t>
+          <t>DIP-PORTABLE ELT 1</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CDY</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HP-1536CMP</t>
+          <t>HP-1716CMP</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1536CMP</t>
+          <t>Boeing 737-8V3 - HP-1716CMP</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4244,34 +4244,44 @@
           <t>DIP</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25-DIP</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>46356.99930555555</v>
+      </c>
       <c r="M41" s="1" t="n">
-        <v>46250.18125</v>
-      </c>
-      <c r="N41" s="1" t="n">
-        <v>46256.99930555555</v>
+        <v>46213.01388888889</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46253</v>
+        <v>46216</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="b">
-        <v>0</v>
-      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>T/A aperturado correctamente // Fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
@@ -4279,11 +4289,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T40S009DNSD</t>
+          <t>T40S0099G88</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4292,30 +4302,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FWD POB</t>
+          <t>DIP | AHM - BLEED CTRL CARD</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CDY</t>
+          <t>HOUR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ACTV</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HP-1831CMP</t>
+          <t>HP-9925CMP</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1831CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9925CMP</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4323,31 +4333,41 @@
           <t>DIP</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>36-DIP</t>
+        </is>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>46220.99930555555</v>
+      </c>
       <c r="M42" s="1" t="n">
-        <v>46250.25069444445</v>
+        <v>46212.89027777778</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>46295.99930555555</v>
+        <v>46214.16666666666</v>
       </c>
       <c r="O42" t="n">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Datos</t>
+          <t>Busqueda</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46253</v>
+        <v>46216</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>NO MENCIONA INTERVALS - REVISAR AMM TASK 36-00-00-710-801 REV. 28- 15-MAY-26</t>
+        </is>
+      </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
@@ -4358,11 +4378,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T40S009DS8C</t>
+          <t>T40S009DDKJ</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4371,11 +4391,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FDR - REPORT</t>
+          <t>DIP-CREW OXYGEN BOTTLE WITH PRESSURE OF 950 PSI</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4389,12 +4409,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HP-9812CMP</t>
+          <t>HP-1376CMP</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9812CMP</t>
+          <t>Boeing 737-7V3 - HP-1376CMP</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4402,16 +4422,22 @@
           <t>DIP</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>35-DIP</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>46250.99930555555</v>
+      </c>
       <c r="M43" s="1" t="n">
-        <v>46251.30277777778</v>
+        <v>46247.62430555555</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>46281.99930555555</v>
+        <v>46248.83333333334</v>
       </c>
       <c r="O43" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -4419,16 +4445,20 @@
         </is>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DIP ACTIVE. T/A aperturado correctamente</t>
+        </is>
+      </c>
       <c r="T43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
@@ -4437,11 +4467,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T40S009DYCU</t>
+          <t>T40S009DFZ5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4450,11 +4480,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIP-AFT UNIVERSAL PRECAUTION KIT</t>
+          <t>WATER EXTINGUISHER BOTTLE</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4468,12 +4498,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HP-9921CMP</t>
+          <t>HP-1729CMP</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9921CMP</t>
+          <t>Boeing 737-8V3 - HP-1729CMP</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4481,16 +4511,20 @@
           <t>DIP</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26-DIP</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>46283.99930555555</v>
+      </c>
       <c r="M44" s="1" t="n">
-        <v>46252.73611111111</v>
-      </c>
-      <c r="N44" s="1" t="n">
-        <v>46356.99930555555</v>
-      </c>
+        <v>46248.25972222222</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4498,14 +4532,18 @@
         </is>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DIP ACTIVE. T/A Aperturado correctamente</t>
+        </is>
+      </c>
       <c r="T44" t="b">
         <v>0</v>
       </c>
@@ -4516,11 +4554,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T40S009DYT0</t>
+          <t>T40S009DHFV</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4529,11 +4567,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIP - RE-TORQUE CENTER TANK ACCESS DOORS 531AB &amp; 531BB MOUNTING BOLTS WITHIN 60 DAYS</t>
+          <t>DIP-25 UNIVERSAL PRECAUTION KIT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4547,12 +4585,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HP-9911CMP</t>
+          <t>HP-9812CMP</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9911CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9812CMP</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4563,13 +4601,13 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="1" t="n">
-        <v>46252.83125</v>
+        <v>46248.65625</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>46309.99930555555</v>
+        <v>46356.99930555555</v>
       </c>
       <c r="O45" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -4581,7 +4619,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>DISCREPANCIA NO CRÍTICA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
@@ -4595,13 +4633,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T40S009E386</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>T40S009DN7C</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>25</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -4610,13 +4646,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FDR -Report</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>DIP-CURRENT CERTIFICATE OF FUMIGATION</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4630,12 +4664,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HP-9808CMP</t>
+          <t>HP-1536CMP</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Boeing 737-8 MAX8 - HP-9808CMP</t>
+          <t>Boeing 737-8V3 - HP-1536CMP</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4646,17 +4680,13 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="1" t="n">
-        <v>46245.16666666666</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>09/10/2026 23:59</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
+        <v>46250.18125</v>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>46256.99930555555</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4664,7 +4694,7 @@
         </is>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4682,13 +4712,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T40S009E3QN</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>T40S009DTD3</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>27</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -4697,13 +4725,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DIP- AFT UNIVERSAL PRECAUTION KI S/N AB8 DUE DATE 30-NOV-2026</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+          <t>DIP- RUDDER CONTROL CABLE RE TENSION CHECK</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4717,12 +4743,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HP-1715CMP</t>
+          <t>HP-1990WWP</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1715CMP</t>
+          <t>Boeing 737-8BK - HP-1990WWP</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4733,21 +4759,25 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="1" t="n">
-        <v>46254.40833333333</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+        <v>46251.67569444444</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>46436.99930555555</v>
+      </c>
+      <c r="O47" t="n">
+        <v>185</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Datos</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA NO CRÍTICA</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4761,11 +4791,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T40S00960XC</t>
+          <t>T40S009DV5L</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -4774,11 +4804,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIP- WATER FIRE EXTINGUISHER</t>
+          <t>DIP - CERTIFICATE OF FUMIGATION</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4787,17 +4817,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HP-1532CMP</t>
+          <t>HP-9925CMP</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1532CMP</t>
+          <t>Boeing 737-9 MAX9 - HP-9925CMP</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4808,17 +4838,21 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="1" t="n">
-        <v>46249.46597222222</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+        <v>46252.14027777778</v>
+      </c>
+      <c r="N48" s="1" t="n">
+        <v>46255.99930555555</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Datos</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46249.46597222222</v>
+        <v>46253</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -4836,11 +4870,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>T40S009DMWC</t>
+          <t>T40S009DZYN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -4849,30 +4883,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ENGINE- Engine #2 s/n 960717 LPT NGV Stage #1 One Airfoil Full axial crack , seven Airfoil no full cracks and hole measuring 0.011 sq inch</t>
+          <t>CARGO HANDLING SYSTEM ROLLERS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CYCLES</t>
+          <t>CDY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HP-1822CMP</t>
+          <t>HP-1990WWP</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1822CMP</t>
+          <t>Boeing 737-8BK - HP-1990WWP</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4883,21 +4917,25 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="1" t="n">
-        <v>46250.46736111111</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+        <v>46253.14305555556</v>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>46382.99930555555</v>
+      </c>
+      <c r="O49" t="n">
+        <v>130</v>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Datos</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46250.46736111111</v>
+        <v>46254</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DISCREPANCIA NO CRÍTICA</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
@@ -4911,11 +4949,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T40S009DFVW</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>35</v>
+          <t>T40S009E386</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4924,11 +4964,13 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIP-APU AIR INLET DOOR HOUSING SKIN UPPER CORNER CRACKED</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>3</v>
+          <t>FDR -Report</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4937,17 +4979,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>ACTV</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HP-1825CMP</t>
+          <t>HP-9808CMP</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Boeing 737-8V3 - HP-1825CMP</t>
+          <t>Boeing 737-8 MAX8 - HP-9808CMP</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4958,17 +5000,25 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="1" t="n">
-        <v>46249.10069444445</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+        <v>46245.16666666666</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>09/10/2026 23:59</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Datos</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46249.10069444445</v>
+        <v>46254</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -4986,11 +5036,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T40S009DSD0</t>
+          <t>T40S009DJHW</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4999,11 +5049,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DIP- WATER FIRE EXTINGUISHER</t>
+          <t>361 453 41 (SCHEDULED MAINTENANCE TASK BLEED PM SENSOR 1 L)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5017,12 +5067,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>HP-9904CMP</t>
+          <t>HP-1828CMP</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Boeing 737-9 MAX9 - HP-9904CMP</t>
+          <t>Boeing 737-8V3 - HP-1828CMP</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5033,7 +5083,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="1" t="n">
-        <v>46251.89375</v>
+        <v>46252.53680555556</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -5043,7 +5093,7 @@
         </is>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46251.89375</v>
+        <v>46252.53680555556</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
